--- a/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
+++ b/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0C44DA-DED9-4BBB-8B6F-C5F7606CF885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2192953-A825-4D9C-83DD-DA6C7468C773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>Date</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Apr06,2026+7-42-35PM</t>
-  </si>
-  <si>
-    <t>Apr06,2026+8-34-06PM</t>
   </si>
   <si>
     <t>Apr06,2026+3-42-35PM</t>
@@ -332,9 +329,6 @@
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.182873258171592</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.17751259924537499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1413,7 +1407,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1437,7 +1431,7 @@
         <v>3</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>4</v>
@@ -1482,31 +1476,31 @@
         <v>6.7351546757008799E-3</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1">
         <f>AVERAGE(B2:B22)</f>
-        <v>0.18267560333364488</v>
+        <v>0.18294734039092225</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" ref="Q2:W2" si="0">AVERAGE(C2:C22)</f>
-        <v>1.3297122443146536</v>
+        <v>1.3298830299073778</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="0"/>
-        <v>1.9893252228025607E-4</v>
+        <v>1.9641689197293384E-4</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="0"/>
-        <v>-2.4183179689267822E-4</v>
+        <v>-2.406690132565138E-4</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="0"/>
-        <v>2.9442968523810213</v>
+        <v>2.9204829485196968</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="0"/>
-        <v>42.188654738532726</v>
+        <v>42.309514451961491</v>
       </c>
       <c r="V2" s="1">
         <f t="shared" si="0"/>
@@ -1514,7 +1508,7 @@
       </c>
       <c r="W2" s="1">
         <f t="shared" si="0"/>
-        <v>6.8888381429540596E-3</v>
+        <v>6.860930773074164E-3</v>
       </c>
       <c r="X2" s="1"/>
     </row>
@@ -1547,38 +1541,38 @@
         <v>7.56590628428462E-3</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P3" s="1">
         <f>_xlfn.STDEV.S(B2:B22)</f>
-        <v>2.4639254664298228E-3</v>
+        <v>2.2021208795305301E-3</v>
       </c>
       <c r="Q3" s="1">
         <f t="shared" ref="Q3:W3" si="1">_xlfn.STDEV.S(C2:C22)</f>
-        <v>1.6557806967159854E-3</v>
+        <v>1.5093569546422382E-3</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="1"/>
-        <v>5.1225896370693579E-4</v>
+        <v>5.2616911527482121E-4</v>
       </c>
       <c r="S3" s="1">
         <f t="shared" si="1"/>
-        <v>7.836576513040707E-5</v>
+        <v>8.0335713915932646E-5</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" si="1"/>
-        <v>0.46975070417045095</v>
+        <v>0.47005614267516393</v>
       </c>
       <c r="U3" s="1">
         <f t="shared" si="1"/>
-        <v>1.8608947335225388</v>
+        <v>1.8294651351078743</v>
       </c>
       <c r="V3" s="1">
         <v>0</v>
       </c>
       <c r="W3" s="1">
         <f t="shared" si="1"/>
-        <v>7.5377627846090977E-4</v>
+        <v>7.6374235002039438E-4</v>
       </c>
       <c r="X3" s="1"/>
     </row>
@@ -1611,31 +1605,31 @@
         <v>7.6309500096276399E-3</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P4" s="1">
         <f>P3/P2</f>
-        <v>1.3487983186948211E-2</v>
+        <v>1.2036911139703009E-2</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" ref="Q4:W4" si="2">Q3/Q2</f>
-        <v>1.2452173045675687E-3</v>
+        <v>1.1349546694699609E-3</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="2"/>
-        <v>2.5750388012738585</v>
+        <v>2.6788384134869982</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="2"/>
-        <v>-0.32405070853931078</v>
+        <v>-0.33380165077715224</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" si="2"/>
-        <v>0.15954597233990472</v>
+        <v>0.16095151074702249</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" si="2"/>
-        <v>4.4108890057186462E-2</v>
+        <v>4.3240040893994691E-2</v>
       </c>
       <c r="V4" s="1">
         <f t="shared" si="2"/>
@@ -1643,7 +1637,7 @@
       </c>
       <c r="W4" s="1">
         <f t="shared" si="2"/>
-        <v>0.10941994322103157</v>
+        <v>0.11131760037832095</v>
       </c>
       <c r="X4" s="1"/>
     </row>
@@ -1676,31 +1670,31 @@
         <v>7.6003569767388E-3</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P5" s="1">
-        <f>P4/COUNT(B2:B22) * 100</f>
-        <v>6.7439915934741052E-2</v>
+        <f>P4/SQRT(COUNT(B2:B22)) * 100</f>
+        <v>0.27614568026497055</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" ref="Q5:W5" si="3">Q4/COUNT(C2:C22) * 100</f>
-        <v>6.2260865228378438E-3</v>
+        <v>5.973445628789268E-3</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="3"/>
-        <v>12.875194006369291</v>
+        <v>14.099149544668412</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="3"/>
-        <v>-1.6202535426965541</v>
+        <v>-1.756850793563959</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="3"/>
-        <v>0.79772986169952365</v>
+        <v>0.84711321445801313</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" si="3"/>
-        <v>0.22054445028593231</v>
+        <v>0.22757916259997205</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="3"/>
@@ -1708,13 +1702,13 @@
       </c>
       <c r="W5" s="1">
         <f t="shared" si="3"/>
-        <v>0.54709971610515784</v>
+        <v>0.58588210725432077</v>
       </c>
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>0.17820611212962301</v>
@@ -1743,7 +1737,7 @@
     </row>
     <row r="7" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
         <v>0.18269367018010399</v>
@@ -1772,7 +1766,7 @@
     </row>
     <row r="8" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
         <v>0.184059854518271</v>
@@ -1801,7 +1795,7 @@
     </row>
     <row r="9" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>0.18187437151116301</v>
@@ -1830,7 +1824,7 @@
     </row>
     <row r="10" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
         <v>0.18158579062830699</v>
@@ -1859,7 +1853,7 @@
     </row>
     <row r="11" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1">
         <v>0.18238164023953901</v>
@@ -1888,7 +1882,7 @@
     </row>
     <row r="12" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
         <v>0.183302795041484</v>
@@ -1917,7 +1911,7 @@
     </row>
     <row r="13" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1">
         <v>0.186980807885406</v>
@@ -2158,34 +2152,16 @@
         <v>7.09094427075126E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="1">
-        <v>0.17751259924537499</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.3264673180528901</v>
-      </c>
-      <c r="D22" s="1">
-        <v>2.4672949811937903E-4</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-2.63924685979802E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>3.3967610257461902</v>
-      </c>
-      <c r="G22" s="1">
-        <v>39.892320183386197</v>
-      </c>
-      <c r="H22" s="1">
-        <v>7.5215001461198105E-4</v>
-      </c>
-      <c r="I22" s="1">
-        <v>7.4190781706720797E-3</v>
-      </c>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
+++ b/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2192953-A825-4D9C-83DD-DA6C7468C773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B830098-33C4-4CAE-A9D8-E76B90FE2B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="456" sheetId="1" r:id="rId1"/>
+    <sheet name="894" sheetId="2" r:id="rId2"/>
+    <sheet name="Absoprtion coeff" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'894'!$B$2:$B$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -133,6 +138,15 @@
   <si>
     <t>100*std/mean/sqrt(n)</t>
   </si>
+  <si>
+    <t>Apr06,2026+8-34-06PM</t>
+  </si>
+  <si>
+    <t>456 Alpha</t>
+  </si>
+  <si>
+    <t>894 Alpha</t>
+  </si>
 </sst>
 </file>
 
@@ -207,6 +221,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>456 Absorption Coefficients, April</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> 6</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -269,7 +316,7 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$22</c:f>
+              <c:f>'456'!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -309,26 +356,29 @@
                 <c:pt idx="11">
                   <c:v>0.186980807885406</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="12">
                   <c:v>0.18110325820647299</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="13">
                   <c:v>0.18221791853755001</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="14">
                   <c:v>0.18189745497010401</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="15">
                   <c:v>0.184062040242048</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="16">
                   <c:v>0.180025762751445</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="17">
                   <c:v>0.18513813740551099</c:v>
                 </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.18291958569903399</c:v>
+                </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.182873258171592</c:v>
+                  <c:v>0.17751259924537499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -526,7 +576,401 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>894 Absorption Coefficients, April 6 </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'894'!$B$2:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>9.5841418161231999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5479162076406308</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.5970818557036903</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6542865700352092</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.6819878150686591</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.4147266289739004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.3978793532990501</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.6256080694206307</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.5977887849237504</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.6309507973488007</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.6918732409243802</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6422026281330098</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.6063436583162094</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.6714560570485393</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.4148874433485297</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0544-41CF-9853-E7DDBF5A7558}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1128315007"/>
+        <c:axId val="1128315487"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1128315007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128315487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1128315487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1128315007"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1082,20 +1526,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>663575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>396875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>371475</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>377825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1103,6 +2063,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41FB04B3-FFBA-36F0-017A-0A7F75B7D91E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>250825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DAA28BD-074F-280E-78CD-6FDE66C81B25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1480,27 +2481,27 @@
       </c>
       <c r="P2" s="1">
         <f>AVERAGE(B2:B22)</f>
-        <v>0.18294734039092225</v>
+        <v>0.18267791971001701</v>
       </c>
       <c r="Q2" s="1">
         <f t="shared" ref="Q2:W2" si="0">AVERAGE(C2:C22)</f>
-        <v>1.3298830299073778</v>
+        <v>1.3297062414106158</v>
       </c>
       <c r="R2" s="1">
         <f t="shared" si="0"/>
-        <v>1.9641689197293384E-4</v>
+        <v>1.9891124161462896E-4</v>
       </c>
       <c r="S2" s="1">
         <f t="shared" si="0"/>
-        <v>-2.406690132565138E-4</v>
+        <v>-2.4182654593636691E-4</v>
       </c>
       <c r="T2" s="1">
         <f t="shared" si="0"/>
-        <v>2.9204829485196968</v>
+        <v>2.9442805382833939</v>
       </c>
       <c r="U2" s="1">
         <f t="shared" si="0"/>
-        <v>42.309514451961491</v>
+        <v>42.18865445567134</v>
       </c>
       <c r="V2" s="1">
         <f t="shared" si="0"/>
@@ -1508,7 +2509,7 @@
       </c>
       <c r="W2" s="1">
         <f t="shared" si="0"/>
-        <v>6.860930773074164E-3</v>
+        <v>6.8945684636374013E-3</v>
       </c>
       <c r="X2" s="1"/>
     </row>
@@ -1545,34 +2546,34 @@
       </c>
       <c r="P3" s="1">
         <f>_xlfn.STDEV.S(B2:B22)</f>
-        <v>2.2021208795305301E-3</v>
+        <v>2.4641428319202383E-3</v>
       </c>
       <c r="Q3" s="1">
         <f t="shared" ref="Q3:W3" si="1">_xlfn.STDEV.S(C2:C22)</f>
-        <v>1.5093569546422382E-3</v>
+        <v>1.6600142042475577E-3</v>
       </c>
       <c r="R3" s="1">
         <f t="shared" si="1"/>
-        <v>5.2616911527482121E-4</v>
+        <v>5.1226811092735006E-4</v>
       </c>
       <c r="S3" s="1">
         <f t="shared" si="1"/>
-        <v>8.0335713915932646E-5</v>
+        <v>7.8368030186937184E-5</v>
       </c>
       <c r="T3" s="1">
         <f t="shared" si="1"/>
-        <v>0.47005614267516393</v>
+        <v>0.46972496099172645</v>
       </c>
       <c r="U3" s="1">
         <f t="shared" si="1"/>
-        <v>1.8294651351078743</v>
+        <v>1.8608944075254241</v>
       </c>
       <c r="V3" s="1">
         <v>0</v>
       </c>
       <c r="W3" s="1">
         <f t="shared" si="1"/>
-        <v>7.6374235002039438E-4</v>
+        <v>7.5582642455171488E-4</v>
       </c>
       <c r="X3" s="1"/>
     </row>
@@ -1609,27 +2610,27 @@
       </c>
       <c r="P4" s="1">
         <f>P3/P2</f>
-        <v>1.2036911139703009E-2</v>
+        <v>1.3489002041581268E-2</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" ref="Q4:W4" si="2">Q3/Q2</f>
-        <v>1.1349546694699609E-3</v>
+        <v>1.2484067176269968E-3</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="2"/>
-        <v>2.6788384134869982</v>
+        <v>2.5753602801385118</v>
       </c>
       <c r="S4" s="1">
         <f t="shared" si="2"/>
-        <v>-0.33380165077715224</v>
+        <v>-0.32406711134003696</v>
       </c>
       <c r="T4" s="1">
         <f t="shared" si="2"/>
-        <v>0.16095151074702249</v>
+        <v>0.1595381129223476</v>
       </c>
       <c r="U4" s="1">
         <f t="shared" si="2"/>
-        <v>4.3240040893994691E-2</v>
+        <v>4.4108882625794849E-2</v>
       </c>
       <c r="V4" s="1">
         <f t="shared" si="2"/>
@@ -1637,7 +2638,7 @@
       </c>
       <c r="W4" s="1">
         <f t="shared" si="2"/>
-        <v>0.11131760037832095</v>
+        <v>0.10962635711546184</v>
       </c>
       <c r="X4" s="1"/>
     </row>
@@ -1674,27 +2675,27 @@
       </c>
       <c r="P5" s="1">
         <f>P4/SQRT(COUNT(B2:B22)) * 100</f>
-        <v>0.27614568026497055</v>
+        <v>0.30162325513609156</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" ref="Q5:W5" si="3">Q4/COUNT(C2:C22) * 100</f>
-        <v>5.973445628789268E-3</v>
+        <v>6.2420335881349836E-3</v>
       </c>
       <c r="R5" s="1">
         <f t="shared" si="3"/>
-        <v>14.099149544668412</v>
+        <v>12.876801400692559</v>
       </c>
       <c r="S5" s="1">
         <f t="shared" si="3"/>
-        <v>-1.756850793563959</v>
+        <v>-1.6203355567001847</v>
       </c>
       <c r="T5" s="1">
         <f t="shared" si="3"/>
-        <v>0.84711321445801313</v>
+        <v>0.79769056461173793</v>
       </c>
       <c r="U5" s="1">
         <f t="shared" si="3"/>
-        <v>0.22757916259997205</v>
+        <v>0.22054441312897424</v>
       </c>
       <c r="V5" s="1">
         <f t="shared" si="3"/>
@@ -1702,7 +2703,7 @@
       </c>
       <c r="W5" s="1">
         <f t="shared" si="3"/>
-        <v>0.58588210725432077</v>
+        <v>0.54813178557730924</v>
       </c>
       <c r="X5" s="1"/>
     </row>
@@ -1938,218 +2939,236 @@
         <v>7.5602886495809403E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+    <row r="14" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.18110325820647299</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.3280117156865801</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1.0554048359570701E-3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-3.5831966332869098E-4</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2.9022829955347298</v>
+      </c>
+      <c r="G14" s="1">
+        <v>40.394869752424199</v>
+      </c>
+      <c r="H14" s="1">
+        <v>7.5215001461198105E-4</v>
+      </c>
+      <c r="I14" s="1">
+        <v>7.6606876334252803E-3</v>
+      </c>
     </row>
     <row r="15" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>0.18110325820647299</v>
+        <v>0.18221791853755001</v>
       </c>
       <c r="C15" s="1">
-        <v>1.3280117156865801</v>
+        <v>1.3307358018436699</v>
       </c>
       <c r="D15" s="1">
-        <v>1.0554048359570701E-3</v>
+        <v>-2.6756686243661898E-4</v>
       </c>
       <c r="E15" s="1">
-        <v>-3.5831966332869098E-4</v>
+        <v>-1.89160637831153E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>2.9022829955347298</v>
+        <v>2.4036151928351499</v>
       </c>
       <c r="G15" s="1">
-        <v>40.394869752424199</v>
+        <v>40.414898511610801</v>
       </c>
       <c r="H15" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I15" s="1">
-        <v>7.6606876334252803E-3</v>
+        <v>5.7209321426507599E-3</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>0.18221791853755001</v>
+        <v>0.18189745497010401</v>
       </c>
       <c r="C16" s="1">
-        <v>1.3307358018436699</v>
+        <v>1.32960608050337</v>
       </c>
       <c r="D16" s="1">
-        <v>-2.6756686243661898E-4</v>
+        <v>-6.4689972033568502E-4</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.89160637831153E-4</v>
+        <v>-1.3231603066947699E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>2.4036151928351499</v>
+        <v>2.1517258018596501</v>
       </c>
       <c r="G16" s="1">
-        <v>40.414898511610801</v>
+        <v>41.058141280516097</v>
       </c>
       <c r="H16" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I16" s="1">
-        <v>5.7209321426507599E-3</v>
+        <v>7.75233473004815E-3</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>0.18189745497010401</v>
+        <v>0.184062040242048</v>
       </c>
       <c r="C17" s="1">
-        <v>1.32960608050337</v>
+        <v>1.3282334830323801</v>
       </c>
       <c r="D17" s="1">
-        <v>-6.4689972033568502E-4</v>
+        <v>4.7127132113047599E-4</v>
       </c>
       <c r="E17" s="1">
-        <v>-1.3231603066947699E-4</v>
+        <v>-2.8072430656648399E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>2.1517258018596501</v>
+        <v>2.5940882747943799</v>
       </c>
       <c r="G17" s="1">
-        <v>41.058141280516097</v>
+        <v>42.519224223624498</v>
       </c>
       <c r="H17" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I17" s="1">
-        <v>7.75233473004815E-3</v>
+        <v>6.54823852382361E-3</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1">
-        <v>0.184062040242048</v>
+        <v>0.180025762751445</v>
       </c>
       <c r="C18" s="1">
-        <v>1.3282334830323801</v>
+        <v>1.32737352526119</v>
       </c>
       <c r="D18" s="1">
-        <v>4.7127132113047599E-4</v>
+        <v>4.4838362411142102E-4</v>
       </c>
       <c r="E18" s="1">
-        <v>-2.8072430656648399E-4</v>
+        <v>-2.7550782503360798E-4</v>
       </c>
       <c r="F18" s="1">
-        <v>2.5940882747943799</v>
+        <v>2.4033895220102401</v>
       </c>
       <c r="G18" s="1">
-        <v>42.519224223624498</v>
+        <v>40.599731474114201</v>
       </c>
       <c r="H18" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I18" s="1">
-        <v>6.54823852382361E-3</v>
+        <v>6.9993940836831497E-3</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1">
-        <v>0.180025762751445</v>
+        <v>0.18513813740551099</v>
       </c>
       <c r="C19" s="1">
-        <v>1.32737352526119</v>
-      </c>
-      <c r="D19" s="1">
-        <v>4.4838362411142102E-4</v>
+        <v>1.3294356006014201</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-8.0898008405581702E-5</v>
       </c>
       <c r="E19" s="1">
-        <v>-2.7550782503360798E-4</v>
+        <v>-1.6621355476127399E-4</v>
       </c>
       <c r="F19" s="1">
-        <v>2.4033895220102401</v>
+        <v>3.6618855286505099</v>
       </c>
       <c r="G19" s="1">
-        <v>40.599731474114201</v>
+        <v>44.279979789896601</v>
       </c>
       <c r="H19" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I19" s="1">
-        <v>6.9993940836831497E-3</v>
+        <v>5.9458786636464398E-3</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
-        <v>0.18513813740551099</v>
+        <v>0.18291958569903399</v>
       </c>
       <c r="C20" s="1">
-        <v>1.3294356006014201</v>
+        <v>1.32853845389109</v>
       </c>
       <c r="D20" s="2">
-        <v>-8.0898008405581702E-5</v>
+        <v>-1.04713229981422E-5</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.6621355476127399E-4</v>
+        <v>-2.0966247719164999E-4</v>
       </c>
       <c r="F20" s="1">
-        <v>3.6618855286505099</v>
+        <v>3.6482967559267601</v>
       </c>
       <c r="G20" s="1">
-        <v>44.279979789896601</v>
+        <v>44.2260947624534</v>
       </c>
       <c r="H20" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I20" s="1">
-        <v>5.9458786636464398E-3</v>
+        <v>7.2055506844181001E-3</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1">
-        <v>0.182873258171592</v>
+        <v>0.17751259924537499</v>
       </c>
       <c r="C21" s="1">
-        <v>1.3286585119718499</v>
-      </c>
-      <c r="D21" s="2">
-        <v>-1.00457096855994E-5</v>
+        <v>1.3264673180528901</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2.4672949811937903E-4</v>
       </c>
       <c r="E21" s="1">
-        <v>-2.0976749631787601E-4</v>
+        <v>-2.63924685979802E-4</v>
       </c>
       <c r="F21" s="1">
-        <v>3.6486230378793101</v>
+        <v>3.3967610257461902</v>
       </c>
       <c r="G21" s="1">
-        <v>44.226100419681103</v>
+        <v>39.892320183386197</v>
       </c>
       <c r="H21" s="1">
         <v>7.5215001461198105E-4</v>
       </c>
       <c r="I21" s="1">
-        <v>7.09094427075126E-3</v>
+        <v>7.4190781706720797E-3</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -2167,4 +3186,710 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD5E8C4A-68F1-499A-92AA-6A03568091AB}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>9.5841418161231999</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.16785616842497</v>
+      </c>
+      <c r="D2" s="1">
+        <v>-1.14062824653226E-3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2.8625496556513701</v>
+      </c>
+      <c r="F2" s="1">
+        <v>42.367934428925402</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H2" s="1">
+        <v>3.91488810011313E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>9.5479162076406308</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1.1666630967512499</v>
+      </c>
+      <c r="D3" s="1">
+        <v>-9.7420467527509203E-4</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.8621893012066901</v>
+      </c>
+      <c r="F3" s="1">
+        <v>41.845628511382401</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3.8679785210545499E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9.5970818557036903</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.16654765543585</v>
+      </c>
+      <c r="D4" s="1">
+        <v>-9.6777866324870702E-4</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2.8626461951264801</v>
+      </c>
+      <c r="F4" s="1">
+        <v>41.752318570743903</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3.84371836522455E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>9.6542865700352092</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.16494906234313</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-5.8279396717671704E-4</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2.8626342369496802</v>
+      </c>
+      <c r="F5" s="1">
+        <v>40.448117925041799</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3.8844470972722103E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
+        <v>9.6819878150686591</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.16566651091161</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-1.47614749092091E-3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2.8608294081244998</v>
+      </c>
+      <c r="F6" s="1">
+        <v>42.722775088650103</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4.0980222460392603E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>9.4147266289739004</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.1679678092972301</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-4.3491298821636999E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.8619396151332199</v>
+      </c>
+      <c r="F7" s="1">
+        <v>42.662536521697398</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3.8909036436339001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1">
+        <v>9.3978793532990501</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.16530776913967</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-1.3679734741703299E-3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2.3619852827147501</v>
+      </c>
+      <c r="F8" s="1">
+        <v>43.5675544619112</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3.8435390387716498E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1">
+        <v>9.6256080694206307</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.16312872806588</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-1.3557706726415901E-3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2.8622869621451601</v>
+      </c>
+      <c r="F9" s="1">
+        <v>42.204033591397703</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4.0124607725458297E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.5977887849237504</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.1606770778392601</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-2.0224711289164501E-3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2.8621420786566998</v>
+      </c>
+      <c r="F10" s="1">
+        <v>43.911338034350102</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.0161020680797598E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9.6309507973488007</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.1599040984425</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-1.6396888009149999E-3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2.86327561746144</v>
+      </c>
+      <c r="F11" s="1">
+        <v>42.333341404611602</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4.01957931520791E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1">
+        <v>9.6918732409243802</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.1564926066172201</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-1.5183837562695E-3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2.36242151745728</v>
+      </c>
+      <c r="F12" s="1">
+        <v>40.908696174550201</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.0627807408899798E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>9.6422026281330098</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1.1558310900464801</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-1.19798866240016E-3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2.8622893746945501</v>
+      </c>
+      <c r="F13" s="1">
+        <v>42.528938193702302</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3.99250596686112E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9.6063436583162094</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1.1558285076978201</v>
+      </c>
+      <c r="D14" s="1">
+        <v>-1.3719773803203201E-3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2.8625253822498098</v>
+      </c>
+      <c r="F14" s="1">
+        <v>42.581812179514799</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3.9800795650306101E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>9.6714560570485393</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.15194000942507</v>
+      </c>
+      <c r="D15" s="1">
+        <v>-8.0045689220126801E-4</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.3620085335246499</v>
+      </c>
+      <c r="F15" s="1">
+        <v>42.006235753904797</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4.0275235987477398E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>9.4148874433485297</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.16954164980798</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-3.2814577453933697E-4</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2.8617460429306898</v>
+      </c>
+      <c r="F16" s="1">
+        <v>43.029248910051798</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3.6655798700973699E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>9.5342199610622096</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1.1690871202206099</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1.4234729456167301E-4</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.8621122707985802</v>
+      </c>
+      <c r="F17" s="1">
+        <v>40.528247168413799</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2.2873004957014E-3</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3.6961030341406902E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069855D0-5652-4354-B9CB-3CB4F2CA0E80}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.18709784436360999</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9.5841418161231999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.182062561992865</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1">
+        <v>9.5479162076406308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.18300790529903599</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9.5970818557036903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.18542828335339201</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
+        <v>9.6542865700352092</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.17820611212962301</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9.6819878150686591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.18269367018010399</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>9.4147266289739004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.184059854518271</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9.3978793532990501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.18187437151116301</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9.6256080694206307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0.18238164023953901</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9.5977887849237504</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1">
+        <v>0.183302795041484</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9.6309507973488007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0.186980807885406</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.6918732409243802</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0.18110325820647299</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1">
+        <v>9.6422026281330098</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.18221791853755001</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1">
+        <v>9.6063436583162094</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.184062040242048</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1">
+        <v>9.6714560570485393</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.18513813740551099</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9.4148874433485297</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.18291958569903399</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1">
+        <v>9.5342199610622096</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
+++ b/BeatnotePostCombFix/Apr06,2026/456Quad_fit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2192953-A825-4D9C-83DD-DA6C7468C773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6D7122-23FE-4C73-86A2-D376424E4C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -484,7 +485,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -492,6 +492,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1087,15 +1088,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>390525</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>561975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>371475</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>323850</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1387,13 +1388,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="15" max="15" width="23.54296875" customWidth="1"/>
-    <col min="16" max="16" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1448,7 @@
       </c>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1512,7 +1513,7 @@
       </c>
       <c r="X2" s="1"/>
     </row>
-    <row r="3" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1576,7 +1577,7 @@
       </c>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1641,7 +1642,7 @@
       </c>
       <c r="X4" s="1"/>
     </row>
-    <row r="5" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1706,7 +1707,7 @@
       </c>
       <c r="X5" s="1"/>
     </row>
-    <row r="6" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1735,7 +1736,7 @@
         <v>6.5353645471448799E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>6.0453225617137204E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>6.3505393389513597E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -1822,7 +1823,7 @@
         <v>6.7569254269072903E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -1851,7 +1852,7 @@
         <v>7.8301685001272402E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1880,7 +1881,7 @@
         <v>6.7890161662815703E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -1909,7 +1910,7 @@
         <v>5.2392815033215001E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>7.5602886495809403E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1949,7 +1950,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>7.6606876334252803E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -2007,7 +2008,7 @@
         <v>5.7209321426507599E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -2036,7 +2037,7 @@
         <v>7.75233473004815E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>15</v>
       </c>
@@ -2065,7 +2066,7 @@
         <v>6.54823852382361E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>16</v>
       </c>
@@ -2094,7 +2095,7 @@
         <v>6.9993940836831497E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>5.9458786636464398E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
@@ -2152,7 +2153,7 @@
         <v>7.09094427075126E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
